--- a/output/tables/port_stats_1_120_50.xlsx
+++ b/output/tables/port_stats_1_120_50.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,48 +662,64 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>B_UMD</t>
+          <t>t_HML</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3311427509652338</v>
+        <v>7.269149118637875</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.4911438545488206</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1162137493597864</v>
+        <v>6.567720366630852</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>t_UMD</t>
+          <t>B_UMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.114103950879617</v>
+        <v>-0.3311427509652338</v>
       </c>
       <c r="C16" t="n">
-        <v>2.343657160662783</v>
+        <v>0.1015017459043074</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.113995257341653</v>
+        <v>-0.1162137493597864</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>t_UMD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-3.114103950879617</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.343657160662783</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.113995257341653</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>R_SQUARED</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>0.6086513825931629</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>0.2136196510592738</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>0.3877287493977855</v>
       </c>
     </row>
